--- a/case_studies/2050/technologies.xlsx
+++ b/case_studies/2050/technologies.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\2050\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87F2D478-B674-40BB-A618-125BC60FC7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999BD818-85CC-4B11-B4BB-9CF33A65E173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="6168" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="existing" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="38">
   <si>
     <t>cluster</t>
   </si>
@@ -120,6 +120,21 @@
   </si>
   <si>
     <t>NL4</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_BE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_DE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_NL</t>
+  </si>
+  <si>
+    <t>H2_network_connection_in</t>
+  </si>
+  <si>
+    <t>H2_network_connection_out</t>
   </si>
 </sst>
 </file>
@@ -517,8 +532,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -546,7 +561,7 @@
     <col min="25" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -625,8 +640,23 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
@@ -705,8 +735,23 @@
       <c r="Z2" s="3">
         <v>0</v>
       </c>
+      <c r="AA2">
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -785,8 +830,23 @@
       <c r="Z3" s="5">
         <v>0</v>
       </c>
+      <c r="AA3">
+        <v>0</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -865,8 +925,23 @@
       <c r="Z4" s="3">
         <v>0</v>
       </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -945,8 +1020,23 @@
       <c r="Z5" s="5">
         <v>0</v>
       </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1025,8 +1115,23 @@
       <c r="Z6" s="3">
         <v>0</v>
       </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>0</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
@@ -1105,8 +1210,23 @@
       <c r="Z7" s="5">
         <v>0</v>
       </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -1183,6 +1303,21 @@
         <v>0</v>
       </c>
       <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
         <v>0</v>
       </c>
     </row>
@@ -1193,8 +1328,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3653B6C3-1F25-449A-8ECB-65DFB48DAFBD}">
-  <dimension ref="A1:Z8"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AE8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -1222,7 +1357,7 @@
     <col min="25" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1301,8 +1436,23 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>37</v>
+      </c>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>26</v>
       </c>
@@ -1381,8 +1531,23 @@
       <c r="Z2" s="3">
         <v>1</v>
       </c>
+      <c r="AA2">
+        <v>1</v>
+      </c>
+      <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <v>0</v>
+      </c>
     </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>27</v>
       </c>
@@ -1461,8 +1626,23 @@
       <c r="Z3" s="5">
         <v>1</v>
       </c>
+      <c r="AA3">
+        <v>1</v>
+      </c>
+      <c r="AB3">
+        <v>0</v>
+      </c>
+      <c r="AC3">
+        <v>0</v>
+      </c>
+      <c r="AD3">
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>28</v>
       </c>
@@ -1541,8 +1721,23 @@
       <c r="Z4" s="3">
         <v>1</v>
       </c>
+      <c r="AA4">
+        <v>0</v>
+      </c>
+      <c r="AB4">
+        <v>1</v>
+      </c>
+      <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <v>0</v>
+      </c>
+      <c r="AE4">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>29</v>
       </c>
@@ -1621,8 +1816,23 @@
       <c r="Z5" s="5">
         <v>1</v>
       </c>
+      <c r="AA5">
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <v>1</v>
+      </c>
+      <c r="AD5">
+        <v>0</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>30</v>
       </c>
@@ -1701,8 +1911,23 @@
       <c r="Z6" s="3">
         <v>1</v>
       </c>
+      <c r="AA6">
+        <v>0</v>
+      </c>
+      <c r="AB6">
+        <v>0</v>
+      </c>
+      <c r="AC6">
+        <v>1</v>
+      </c>
+      <c r="AD6">
+        <v>0</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>31</v>
       </c>
@@ -1781,8 +2006,23 @@
       <c r="Z7" s="5">
         <v>1</v>
       </c>
+      <c r="AA7">
+        <v>0</v>
+      </c>
+      <c r="AB7">
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <v>1</v>
+      </c>
+      <c r="AD7">
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>32</v>
       </c>
@@ -1860,6 +2100,21 @@
       </c>
       <c r="Z8" s="3">
         <v>1</v>
+      </c>
+      <c r="AA8">
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/case_studies/2050/technologies.xlsx
+++ b/case_studies/2050/technologies.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\2050\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{999BD818-85CC-4B11-B4BB-9CF33A65E173}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6BDA0F-FBDF-4836-8A32-04BEC6B77DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,6 +101,21 @@
     <t>CO2toEmissions</t>
   </si>
   <si>
+    <t>electricity_grid_connection_BE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_DE</t>
+  </si>
+  <si>
+    <t>electricity_grid_connection_NL</t>
+  </si>
+  <si>
+    <t>H2_network_connection_in</t>
+  </si>
+  <si>
+    <t>H2_network_connection_out</t>
+  </si>
+  <si>
     <t>BEL1</t>
   </si>
   <si>
@@ -120,21 +135,6 @@
   </si>
   <si>
     <t>NL4</t>
-  </si>
-  <si>
-    <t>electricity_grid_connection_BE</t>
-  </si>
-  <si>
-    <t>electricity_grid_connection_DE</t>
-  </si>
-  <si>
-    <t>electricity_grid_connection_NL</t>
-  </si>
-  <si>
-    <t>H2_network_connection_in</t>
-  </si>
-  <si>
-    <t>H2_network_connection_out</t>
   </si>
 </sst>
 </file>
@@ -559,6 +559,9 @@
     <col min="23" max="23" width="11" customWidth="1"/>
     <col min="24" max="24" width="15" customWidth="1"/>
     <col min="25" max="26" width="16" customWidth="1"/>
+    <col min="27" max="29" width="32" customWidth="1"/>
+    <col min="30" max="30" width="26" customWidth="1"/>
+    <col min="31" max="31" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -640,31 +643,31 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>37</v>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3">
         <v>0</v>
       </c>
       <c r="C2" s="3">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="D2" s="3">
         <v>0</v>
@@ -673,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="3">
-        <v>0.01</v>
+        <v>17.75</v>
       </c>
       <c r="G2" s="3">
         <v>0</v>
@@ -685,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="3">
-        <v>255.87</v>
+        <v>248.31</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -703,10 +706,10 @@
         <v>0</v>
       </c>
       <c r="P2" s="3">
-        <v>135.49</v>
+        <v>170.14</v>
       </c>
       <c r="Q2" s="3">
-        <v>184.21</v>
+        <v>218.87</v>
       </c>
       <c r="R2" s="3">
         <v>0</v>
@@ -724,10 +727,10 @@
         <v>39.340000000000003</v>
       </c>
       <c r="W2" s="3">
-        <v>251.22</v>
+        <v>245.72</v>
       </c>
       <c r="X2" s="3">
-        <v>444.12</v>
+        <v>56.18</v>
       </c>
       <c r="Y2" s="3">
         <v>0</v>
@@ -735,31 +738,31 @@
       <c r="Z2" s="3">
         <v>0</v>
       </c>
-      <c r="AA2">
-        <v>0</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
+      <c r="AA2" s="3">
+        <v>2100.29</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE2" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B3" s="5">
         <v>0</v>
       </c>
       <c r="C3" s="5">
-        <v>0</v>
+        <v>1964.78</v>
       </c>
       <c r="D3" s="5">
         <v>0</v>
@@ -768,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5">
-        <v>6.63</v>
+        <v>0.03</v>
       </c>
       <c r="G3" s="5">
         <v>0</v>
@@ -830,25 +833,25 @@
       <c r="Z3" s="5">
         <v>0</v>
       </c>
-      <c r="AA3">
-        <v>0</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
+      <c r="AA3" s="5">
+        <v>1933.26</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>4.7699999999999996</v>
+      </c>
+      <c r="AE3" s="5">
+        <v>30.6</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>0</v>
@@ -863,25 +866,25 @@
         <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>1.32</v>
+        <v>50.85</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
       </c>
       <c r="H4" s="3">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I4" s="3">
         <v>0</v>
       </c>
       <c r="J4" s="3">
-        <v>181.13</v>
+        <v>389.78</v>
       </c>
       <c r="K4" s="3">
-        <v>5.36</v>
+        <v>64.34</v>
       </c>
       <c r="L4" s="3">
-        <v>0</v>
+        <v>38.01</v>
       </c>
       <c r="M4" s="3">
         <v>0</v>
@@ -893,13 +896,13 @@
         <v>0</v>
       </c>
       <c r="P4" s="3">
-        <v>155.94</v>
+        <v>388.71</v>
       </c>
       <c r="Q4" s="3">
-        <v>215.39</v>
+        <v>456.17</v>
       </c>
       <c r="R4" s="3">
-        <v>175.71</v>
+        <v>380.67</v>
       </c>
       <c r="S4" s="3">
         <v>43.32</v>
@@ -914,10 +917,10 @@
         <v>11.05</v>
       </c>
       <c r="W4" s="3">
-        <v>172.7</v>
+        <v>377.67</v>
       </c>
       <c r="X4" s="3">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="Y4" s="3">
         <v>0</v>
@@ -925,31 +928,31 @@
       <c r="Z4" s="3">
         <v>0</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>0</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
+      <c r="AA4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>510.85</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>76.28</v>
+      </c>
+      <c r="AE4" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B5" s="5">
-        <v>632.13</v>
+        <v>0</v>
       </c>
       <c r="C5" s="5">
-        <v>1220.4000000000001</v>
+        <v>0</v>
       </c>
       <c r="D5" s="5">
         <v>0</v>
@@ -964,19 +967,19 @@
         <v>0</v>
       </c>
       <c r="H5" s="5">
-        <v>0.53</v>
+        <v>5.98</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
       </c>
       <c r="J5" s="5">
-        <v>0</v>
+        <v>198.78</v>
       </c>
       <c r="K5" s="5">
-        <v>0</v>
+        <v>163.36000000000001</v>
       </c>
       <c r="L5" s="5">
-        <v>0</v>
+        <v>110.53</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
@@ -988,10 +991,10 @@
         <v>0</v>
       </c>
       <c r="P5" s="5">
-        <v>0</v>
+        <v>76.73</v>
       </c>
       <c r="Q5" s="5">
-        <v>0</v>
+        <v>84.4</v>
       </c>
       <c r="R5" s="5">
         <v>0</v>
@@ -1000,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="5">
-        <v>0</v>
+        <v>110.53</v>
       </c>
       <c r="U5" s="5">
         <v>0</v>
@@ -1009,7 +1012,7 @@
         <v>0</v>
       </c>
       <c r="W5" s="5">
-        <v>0</v>
+        <v>189.3</v>
       </c>
       <c r="X5" s="5">
         <v>0</v>
@@ -1020,31 +1023,31 @@
       <c r="Z5" s="5">
         <v>0</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>0</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
+      <c r="AA5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="5">
+        <v>601.29999999999995</v>
+      </c>
+      <c r="AD5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3">
-        <v>1144.48</v>
+        <v>469.01</v>
       </c>
       <c r="C6" s="3">
-        <v>544.5</v>
+        <v>444.62</v>
       </c>
       <c r="D6" s="3">
         <v>0</v>
@@ -1053,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3">
-        <v>7.92</v>
+        <v>17.78</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -1065,13 +1068,13 @@
         <v>0</v>
       </c>
       <c r="J6" s="3">
-        <v>120.5</v>
+        <v>113.82</v>
       </c>
       <c r="K6" s="3">
         <v>0</v>
       </c>
       <c r="L6" s="3">
-        <v>0</v>
+        <v>23.14</v>
       </c>
       <c r="M6" s="3">
         <v>0</v>
@@ -1083,13 +1086,13 @@
         <v>0</v>
       </c>
       <c r="P6" s="3">
-        <v>72.67</v>
+        <v>139.33000000000001</v>
       </c>
       <c r="Q6" s="3">
-        <v>72.67</v>
+        <v>139.37</v>
       </c>
       <c r="R6" s="3">
-        <v>116.62</v>
+        <v>116.66</v>
       </c>
       <c r="S6" s="3">
         <v>0</v>
@@ -1115,31 +1118,31 @@
       <c r="Z6" s="3">
         <v>0</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>0</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
+      <c r="AA6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>1071.04</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>21.22</v>
+      </c>
+      <c r="AE6" s="3">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B7" s="5">
         <v>0</v>
       </c>
       <c r="C7" s="5">
-        <v>1239.69</v>
+        <v>21.22</v>
       </c>
       <c r="D7" s="5">
         <v>0</v>
@@ -1210,28 +1213,28 @@
       <c r="Z7" s="5">
         <v>0</v>
       </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>0</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
+      <c r="AA7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>22.17</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="5">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3">
-        <v>803.86</v>
+        <v>0</v>
       </c>
       <c r="C8" s="3">
         <v>0</v>
@@ -1258,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="K8" s="3">
-        <v>0</v>
+        <v>30.42</v>
       </c>
       <c r="L8" s="3">
-        <v>30.92</v>
+        <v>180.55</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -1273,31 +1276,31 @@
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>62.67</v>
+        <v>279.01</v>
       </c>
       <c r="Q8" s="3">
-        <v>115.16</v>
+        <v>323.79000000000002</v>
       </c>
       <c r="R8" s="3">
         <v>0</v>
       </c>
       <c r="S8" s="3">
-        <v>35.39</v>
+        <v>30.17</v>
       </c>
       <c r="T8" s="3">
-        <v>2.14</v>
+        <v>143.97</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="W8" s="3">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="X8" s="3">
-        <v>136.33000000000001</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
@@ -1305,20 +1308,20 @@
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>0</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>519.07000000000005</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>7.15</v>
       </c>
     </row>
   </sheetData>
@@ -1327,7 +1330,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3653B6C3-1F25-449A-8ECB-65DFB48DAFBD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BDE9BCA-3CC4-4E74-8992-63088FB367A4}">
   <dimension ref="A1:AE8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -1355,6 +1358,9 @@
     <col min="23" max="23" width="11" customWidth="1"/>
     <col min="24" max="24" width="15" customWidth="1"/>
     <col min="25" max="26" width="16" customWidth="1"/>
+    <col min="27" max="29" width="32" customWidth="1"/>
+    <col min="30" max="30" width="26" customWidth="1"/>
+    <col min="31" max="31" width="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:31" ht="18" customHeight="1" x14ac:dyDescent="0.3">
@@ -1436,25 +1442,25 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AE1" t="s">
-        <v>37</v>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3">
         <v>1</v>
@@ -1531,25 +1537,25 @@
       <c r="Z2" s="3">
         <v>1</v>
       </c>
-      <c r="AA2">
-        <v>1</v>
-      </c>
-      <c r="AB2">
-        <v>0</v>
-      </c>
-      <c r="AC2">
-        <v>0</v>
-      </c>
-      <c r="AD2">
-        <v>0</v>
-      </c>
-      <c r="AE2">
-        <v>0</v>
+      <c r="AA2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC2" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD2" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
@@ -1626,25 +1632,25 @@
       <c r="Z3" s="5">
         <v>1</v>
       </c>
-      <c r="AA3">
-        <v>1</v>
-      </c>
-      <c r="AB3">
-        <v>0</v>
-      </c>
-      <c r="AC3">
-        <v>0</v>
-      </c>
-      <c r="AD3">
-        <v>0</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
+      <c r="AA3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC3" s="5">
+        <v>0</v>
+      </c>
+      <c r="AD3" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>1</v>
@@ -1721,25 +1727,25 @@
       <c r="Z4" s="3">
         <v>1</v>
       </c>
-      <c r="AA4">
-        <v>0</v>
-      </c>
-      <c r="AB4">
-        <v>1</v>
-      </c>
-      <c r="AC4">
-        <v>0</v>
-      </c>
-      <c r="AD4">
-        <v>0</v>
-      </c>
-      <c r="AE4">
-        <v>0</v>
+      <c r="AA4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD4" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
@@ -1816,25 +1822,25 @@
       <c r="Z5" s="5">
         <v>1</v>
       </c>
-      <c r="AA5">
-        <v>0</v>
-      </c>
-      <c r="AB5">
-        <v>0</v>
-      </c>
-      <c r="AC5">
-        <v>1</v>
-      </c>
-      <c r="AD5">
-        <v>0</v>
-      </c>
-      <c r="AE5">
-        <v>0</v>
+      <c r="AA5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B6" s="3">
         <v>1</v>
@@ -1911,25 +1917,25 @@
       <c r="Z6" s="3">
         <v>1</v>
       </c>
-      <c r="AA6">
-        <v>0</v>
-      </c>
-      <c r="AB6">
-        <v>0</v>
-      </c>
-      <c r="AC6">
-        <v>1</v>
-      </c>
-      <c r="AD6">
-        <v>0</v>
-      </c>
-      <c r="AE6">
-        <v>0</v>
+      <c r="AA6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="3">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="B7" s="5">
         <v>1</v>
@@ -2006,25 +2012,25 @@
       <c r="Z7" s="5">
         <v>1</v>
       </c>
-      <c r="AA7">
-        <v>0</v>
-      </c>
-      <c r="AB7">
-        <v>0</v>
-      </c>
-      <c r="AC7">
-        <v>1</v>
-      </c>
-      <c r="AD7">
-        <v>0</v>
-      </c>
-      <c r="AE7">
-        <v>0</v>
+      <c r="AA7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="5">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="5">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="5">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="5">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3">
         <v>1</v>
@@ -2101,20 +2107,20 @@
       <c r="Z8" s="3">
         <v>1</v>
       </c>
-      <c r="AA8">
-        <v>0</v>
-      </c>
-      <c r="AB8">
-        <v>0</v>
-      </c>
-      <c r="AC8">
-        <v>1</v>
-      </c>
-      <c r="AD8">
-        <v>0</v>
-      </c>
-      <c r="AE8">
-        <v>0</v>
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="3">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="3">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/case_studies/2050/technologies.xlsx
+++ b/case_studies/2050/technologies.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Github\AdOpT-NET0_my\case_studies\2050\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6BDA0F-FBDF-4836-8A32-04BEC6B77DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_FDB96DFE34A4133CF4515CD4235BDA1626C6A626" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="3">
-        <v>17.75</v>
+        <v>6.77</v>
       </c>
       <c r="G2" s="3">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="3">
-        <v>248.31</v>
+        <v>238.79</v>
       </c>
       <c r="K2" s="3">
         <v>0</v>
@@ -706,10 +706,10 @@
         <v>0</v>
       </c>
       <c r="P2" s="3">
-        <v>170.14</v>
+        <v>213.75</v>
       </c>
       <c r="Q2" s="3">
-        <v>218.87</v>
+        <v>262.47000000000003</v>
       </c>
       <c r="R2" s="3">
         <v>0</v>
@@ -727,10 +727,10 @@
         <v>39.340000000000003</v>
       </c>
       <c r="W2" s="3">
-        <v>245.72</v>
+        <v>238.8</v>
       </c>
       <c r="X2" s="3">
-        <v>56.18</v>
+        <v>0</v>
       </c>
       <c r="Y2" s="3">
         <v>0</v>
@@ -739,7 +739,7 @@
         <v>0</v>
       </c>
       <c r="AA2" s="3">
-        <v>2100.29</v>
+        <v>0</v>
       </c>
       <c r="AB2" s="3">
         <v>0</v>
@@ -762,7 +762,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="5">
-        <v>1964.78</v>
+        <v>1964.73</v>
       </c>
       <c r="D3" s="5">
         <v>0</v>
@@ -771,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="5">
-        <v>0.03</v>
+        <v>3.18</v>
       </c>
       <c r="G3" s="5">
         <v>0</v>
@@ -834,7 +834,7 @@
         <v>0</v>
       </c>
       <c r="AA3" s="5">
-        <v>1933.26</v>
+        <v>0</v>
       </c>
       <c r="AB3" s="5">
         <v>0</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="AD3" s="5">
-        <v>4.7699999999999996</v>
+        <v>0</v>
       </c>
       <c r="AE3" s="5">
-        <v>30.6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.3">
@@ -866,7 +866,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="3">
-        <v>50.85</v>
+        <v>104.51</v>
       </c>
       <c r="G4" s="3">
         <v>0</v>
@@ -878,13 +878,13 @@
         <v>0</v>
       </c>
       <c r="J4" s="3">
-        <v>389.78</v>
+        <v>343.25</v>
       </c>
       <c r="K4" s="3">
-        <v>64.34</v>
+        <v>158.74</v>
       </c>
       <c r="L4" s="3">
-        <v>38.01</v>
+        <v>135.93</v>
       </c>
       <c r="M4" s="3">
         <v>0</v>
@@ -896,19 +896,19 @@
         <v>0</v>
       </c>
       <c r="P4" s="3">
-        <v>388.71</v>
+        <v>586.46</v>
       </c>
       <c r="Q4" s="3">
-        <v>456.17</v>
+        <v>653.91999999999996</v>
       </c>
       <c r="R4" s="3">
-        <v>380.67</v>
+        <v>346.18</v>
       </c>
       <c r="S4" s="3">
         <v>43.32</v>
       </c>
       <c r="T4" s="3">
-        <v>0</v>
+        <v>128.11000000000001</v>
       </c>
       <c r="U4" s="3">
         <v>0</v>
@@ -917,28 +917,28 @@
         <v>11.05</v>
       </c>
       <c r="W4" s="3">
-        <v>377.67</v>
+        <v>343.17</v>
       </c>
       <c r="X4" s="3">
-        <v>740</v>
+        <v>515.78</v>
       </c>
       <c r="Y4" s="3">
         <v>0</v>
       </c>
       <c r="Z4" s="3">
-        <v>0</v>
+        <v>70.16</v>
       </c>
       <c r="AA4" s="3">
         <v>0</v>
       </c>
       <c r="AB4" s="3">
-        <v>510.85</v>
+        <v>0</v>
       </c>
       <c r="AC4" s="3">
         <v>0</v>
       </c>
       <c r="AD4" s="3">
-        <v>76.28</v>
+        <v>0</v>
       </c>
       <c r="AE4" s="3">
         <v>0</v>
@@ -952,7 +952,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="5">
-        <v>0</v>
+        <v>78.12</v>
       </c>
       <c r="D5" s="5">
         <v>0</v>
@@ -961,7 +961,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="5">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="G5" s="5">
         <v>0</v>
@@ -976,10 +976,10 @@
         <v>198.78</v>
       </c>
       <c r="K5" s="5">
-        <v>163.36000000000001</v>
+        <v>146.59</v>
       </c>
       <c r="L5" s="5">
-        <v>110.53</v>
+        <v>102.64</v>
       </c>
       <c r="M5" s="5">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         <v>0</v>
       </c>
       <c r="T5" s="5">
-        <v>110.53</v>
+        <v>102.64</v>
       </c>
       <c r="U5" s="5">
         <v>0</v>
@@ -1030,7 +1030,7 @@
         <v>0</v>
       </c>
       <c r="AC5" s="5">
-        <v>601.29999999999995</v>
+        <v>0</v>
       </c>
       <c r="AD5" s="5">
         <v>0</v>
@@ -1044,10 +1044,10 @@
         <v>35</v>
       </c>
       <c r="B6" s="3">
-        <v>469.01</v>
+        <v>0</v>
       </c>
       <c r="C6" s="3">
-        <v>444.62</v>
+        <v>1033.24</v>
       </c>
       <c r="D6" s="3">
         <v>0</v>
@@ -1056,7 +1056,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="3">
-        <v>17.78</v>
+        <v>18.559999999999999</v>
       </c>
       <c r="G6" s="3">
         <v>0</v>
@@ -1068,13 +1068,13 @@
         <v>0</v>
       </c>
       <c r="J6" s="3">
-        <v>113.82</v>
+        <v>98.36</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>38.26</v>
       </c>
       <c r="L6" s="3">
-        <v>23.14</v>
+        <v>60.58</v>
       </c>
       <c r="M6" s="3">
         <v>0</v>
@@ -1086,19 +1086,19 @@
         <v>0</v>
       </c>
       <c r="P6" s="3">
-        <v>139.33000000000001</v>
+        <v>210.19</v>
       </c>
       <c r="Q6" s="3">
-        <v>139.37</v>
+        <v>210.23</v>
       </c>
       <c r="R6" s="3">
-        <v>116.66</v>
+        <v>105.43</v>
       </c>
       <c r="S6" s="3">
         <v>0</v>
       </c>
       <c r="T6" s="3">
-        <v>0</v>
+        <v>35.369999999999997</v>
       </c>
       <c r="U6" s="3">
         <v>0</v>
@@ -1107,7 +1107,7 @@
         <v>0</v>
       </c>
       <c r="W6" s="3">
-        <v>116.72</v>
+        <v>105.49</v>
       </c>
       <c r="X6" s="3">
         <v>0</v>
@@ -1125,10 +1125,10 @@
         <v>0</v>
       </c>
       <c r="AC6" s="3">
-        <v>1071.04</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="3">
-        <v>21.22</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="3">
         <v>0</v>
@@ -1142,7 +1142,7 @@
         <v>0</v>
       </c>
       <c r="C7" s="5">
-        <v>21.22</v>
+        <v>90.27</v>
       </c>
       <c r="D7" s="5">
         <v>0</v>
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="5">
-        <v>0</v>
+        <v>5.0199999999999996</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="AC7" s="5">
-        <v>22.17</v>
+        <v>0</v>
       </c>
       <c r="AD7" s="5">
         <v>0</v>
@@ -1237,7 +1237,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="3">
-        <v>0</v>
+        <v>1026.06</v>
       </c>
       <c r="D8" s="3">
         <v>0</v>
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="K8" s="3">
-        <v>30.42</v>
+        <v>0</v>
       </c>
       <c r="L8" s="3">
-        <v>180.55</v>
+        <v>129.29</v>
       </c>
       <c r="M8" s="3">
         <v>0</v>
@@ -1276,31 +1276,31 @@
         <v>0</v>
       </c>
       <c r="P8" s="3">
-        <v>279.01</v>
+        <v>279.02</v>
       </c>
       <c r="Q8" s="3">
         <v>323.79000000000002</v>
       </c>
       <c r="R8" s="3">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="S8" s="3">
         <v>30.17</v>
       </c>
       <c r="T8" s="3">
-        <v>143.97</v>
+        <v>92.71</v>
       </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
       <c r="V8" s="3">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="W8" s="3">
         <v>5.37</v>
       </c>
       <c r="X8" s="3">
-        <v>0</v>
+        <v>136.33000000000001</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
@@ -1315,13 +1315,13 @@
         <v>0</v>
       </c>
       <c r="AC8" s="3">
-        <v>519.07000000000005</v>
+        <v>0</v>
       </c>
       <c r="AD8" s="3">
         <v>0</v>
       </c>
       <c r="AE8" s="3">
-        <v>7.15</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1330,7 +1330,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BDE9BCA-3CC4-4E74-8992-63088FB367A4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AE8"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
